--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.30109250876784</v>
+        <v>7.686427532674775</v>
       </c>
       <c r="D2" t="n">
-        <v>47.56728255058728</v>
+        <v>7.729683414470433</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1977559570321</v>
+        <v>1.819635343017717</v>
       </c>
       <c r="F2" t="n">
-        <v>11.64968016779554</v>
+        <v>1.893073027266775</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.02521319410578</v>
+        <v>6.34159714404219</v>
       </c>
       <c r="D3" t="n">
-        <v>38.17506783575369</v>
+        <v>6.203448523309976</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1977559570321</v>
+        <v>1.819635343017717</v>
       </c>
       <c r="F3" t="n">
-        <v>11.64968016779554</v>
+        <v>1.893073027266775</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.15076938774326</v>
+        <v>3.437000025508281</v>
       </c>
       <c r="D4" t="n">
-        <v>20.3769878900952</v>
+        <v>3.311260532140471</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1977559570321</v>
+        <v>1.819635343017717</v>
       </c>
       <c r="F4" t="n">
-        <v>11.64968016779554</v>
+        <v>1.893073027266775</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.17019203567003</v>
+        <v>8.80265620579638</v>
       </c>
       <c r="D5" t="n">
-        <v>54.71968627703741</v>
+        <v>8.891949020018579</v>
       </c>
       <c r="E5" t="n">
-        <v>11.1977559570321</v>
+        <v>1.819635343017717</v>
       </c>
       <c r="F5" t="n">
-        <v>11.64968016779554</v>
+        <v>1.893073027266775</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.76382440955747</v>
+        <v>5.811621466553089</v>
       </c>
       <c r="D6" t="n">
-        <v>35.67856980839103</v>
+        <v>5.797767593863543</v>
       </c>
       <c r="E6" t="n">
-        <v>11.1977559570321</v>
+        <v>1.819635343017717</v>
       </c>
       <c r="F6" t="n">
-        <v>11.64968016779554</v>
+        <v>1.893073027266775</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
